--- a/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU02/HRM/post DFS_HRM-2031-0360/Panel-28/coupon_back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Coupon_Back_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU02/HRM/post DFS_HRM-2031-0360/Panel-28/coupon_back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Coupon_Back_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.96161</v>
+        <v>16.91291</v>
       </c>
       <c r="D2" t="n">
-        <v>16.79038</v>
+        <v>16.60187</v>
       </c>
       <c r="E2" t="n">
-        <v>16.7468</v>
+        <v>16.76909</v>
       </c>
       <c r="F2" t="n">
-        <v>42.82282</v>
+        <v>42.09354</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0516</v>
+        <v>0.05199</v>
       </c>
       <c r="H2" t="n">
-        <v>1.8033</v>
+        <v>1.78292</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.94018</v>
+        <v>16.80901</v>
       </c>
       <c r="D3" t="n">
-        <v>16.41237</v>
+        <v>16.71418</v>
       </c>
       <c r="E3" t="n">
-        <v>16.60512</v>
+        <v>16.71923</v>
       </c>
       <c r="F3" t="n">
-        <v>42.60938</v>
+        <v>43.08265</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05156</v>
+        <v>0.05009</v>
       </c>
       <c r="H3" t="n">
-        <v>1.80425</v>
+        <v>1.84364</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.7934</v>
+        <v>16.73799</v>
       </c>
       <c r="D4" t="n">
-        <v>16.77755</v>
+        <v>16.62843</v>
       </c>
       <c r="E4" t="n">
-        <v>16.70134</v>
+        <v>16.69025</v>
       </c>
       <c r="F4" t="n">
-        <v>42.4302</v>
+        <v>42.25614</v>
       </c>
       <c r="G4" t="n">
-        <v>0.04999</v>
+        <v>0.05037</v>
       </c>
       <c r="H4" t="n">
-        <v>1.85631</v>
+        <v>1.81032</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>17.04264</v>
+        <v>16.78591</v>
       </c>
       <c r="D6" t="n">
-        <v>15.78383</v>
+        <v>16.01481</v>
       </c>
       <c r="E6" t="n">
-        <v>16.5959</v>
+        <v>16.25881</v>
       </c>
       <c r="F6" t="n">
-        <v>21.92937</v>
+        <v>21.63527</v>
       </c>
       <c r="G6" t="n">
-        <v>34.50899</v>
+        <v>34.72702</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.66636</v>
+        <v>16.50297</v>
       </c>
       <c r="D7" t="n">
-        <v>15.9576</v>
+        <v>16.28932</v>
       </c>
       <c r="E7" t="n">
-        <v>16.22643</v>
+        <v>16.29764</v>
       </c>
       <c r="F7" t="n">
-        <v>21.65534</v>
+        <v>21.82104</v>
       </c>
       <c r="G7" t="n">
-        <v>34.99493</v>
+        <v>34.20938</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.9243</v>
+        <v>16.96926</v>
       </c>
       <c r="D8" t="n">
-        <v>15.78882</v>
+        <v>16.05677</v>
       </c>
       <c r="E8" t="n">
-        <v>16.45227</v>
+        <v>16.32851</v>
       </c>
       <c r="F8" t="n">
-        <v>21.80671</v>
+        <v>21.79768</v>
       </c>
       <c r="G8" t="n">
-        <v>34.37432</v>
+        <v>34.39938</v>
       </c>
     </row>
     <row r="9">
@@ -650,10 +650,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.60221</v>
+        <v>0.6083499999999999</v>
       </c>
       <c r="D10" t="n">
-        <v>1.11287</v>
+        <v>1.10169</v>
       </c>
     </row>
     <row r="11">
@@ -663,10 +663,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.60038</v>
+        <v>0.61564</v>
       </c>
       <c r="D11" t="n">
-        <v>1.13268</v>
+        <v>1.14425</v>
       </c>
     </row>
     <row r="12">
@@ -676,10 +676,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.61464</v>
+        <v>0.60593</v>
       </c>
       <c r="D12" t="n">
-        <v>1.08862</v>
+        <v>1.11329</v>
       </c>
     </row>
   </sheetData>
